--- a/Statistics/200m Rygg_statistics.xlsx
+++ b/Statistics/200m Rygg_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,20 +822,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.19,32</t>
+          <t>2.18,76</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2.44,77</t>
+          <t>2.43,30</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>07.06.2025</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1412,12 +1412,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Scott Rene Høgenhaug</t>
+          <t>Fredrik Tronvoll</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2.26,75</t>
+          <t>2.26,80</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29.01.2017</t>
+          <t>28.10.2012</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fredrik Tronvoll</t>
+          <t>Scott Rene Høgenhaug</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2.26,80</t>
+          <t>2.26,75</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>28.10.2012</t>
+          <t>29.01.2017</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1517,25 +1517,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Birk Skaalvik Trelstad</t>
+          <t>Olav Nygård Bergum</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2.28,64</t>
+          <t>2.27,61</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1552,25 +1552,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Daniel Moen Manriquez</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2.29,04</t>
+          <t>2.28,05</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12.02.2017</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1587,25 +1587,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Carl Victor Mukisa Nygård</t>
+          <t>Birk Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.29,06</t>
+          <t>2.28,64</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1622,25 +1622,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Elias Hauge Lien</t>
+          <t>Daniel Moen Manriquez</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2.29,80</t>
+          <t>2.29,04</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>12.02.2017</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1657,20 +1657,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Carl Victor Mukisa Nygård</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2.29,77</t>
+          <t>2.29,06</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10.02.2013</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1692,20 +1692,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jenny Marandon Natvik</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.48,90</t>
+          <t>2.29,77</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>18.01.2015</t>
+          <t>10.02.2013</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1727,25 +1727,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sander Haugan</t>
+          <t>Elias Hauge Lien</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.30,91</t>
+          <t>2.29,80</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>29.02.2020</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1762,20 +1762,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Iris Elise Moen</t>
+          <t>Jenny Marandon Natvik</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.50,91</t>
+          <t>2.48,90</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>18.01.2015</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1797,25 +1797,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mattias Isaksen</t>
+          <t>Sander Haugan</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.32,38</t>
+          <t>2.30,91</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>29.02.2020</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1832,20 +1832,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tobias Gilbu</t>
+          <t>Iris Elise Moen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.32,27</t>
+          <t>2.50,91</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11.02.2018</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Olav Nygård Bergum</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2.32,25</t>
+          <t>2.32,38</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1902,20 +1902,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Morten Olden Larsen</t>
+          <t>Tobias Gilbu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.32,55</t>
+          <t>2.32,27</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10.02.2013</t>
+          <t>11.02.2018</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1937,25 +1937,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Aksel Viken Refseth</t>
+          <t>Morten Olden Larsen</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.32,80</t>
+          <t>2.32,55</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>10.02.2013</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1972,20 +1972,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Thomas Johansen</t>
+          <t>Aksel Viken Refseth</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.33,35</t>
+          <t>2.32,80</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>08.02.2015</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2007,16 +2007,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jonas Fiskaa Barstad</t>
+          <t>Thomas Johansen</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.33,60</t>
+          <t>2.33,35</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2042,25 +2042,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Jonas Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.33,66</t>
+          <t>2.33,60</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>27.10.2013</t>
+          <t>08.02.2015</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2077,25 +2077,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.33,68</t>
+          <t>2.33,52</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>27.10.2013</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2112,25 +2112,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2.33,88</t>
+          <t>2.33,68</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>27.10.2013</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2147,25 +2147,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sondre Brunvoll Møllerløkken</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2.34,14</t>
+          <t>2.33,66</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>27.10.2013</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2182,25 +2182,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Elian Theodor Kringstad</t>
+          <t>Sondre Brunvoll Møllerløkken</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.34,76</t>
+          <t>2.33,69</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2217,25 +2217,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hasith Ransiri Attanapola</t>
+          <t>Elian Theodor Kringstad</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2.35,04</t>
+          <t>2.34,76</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2252,25 +2252,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lionel Nicolas Weissbrodt</t>
+          <t>Hasith Ransiri Attanapola</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2.35,10</t>
+          <t>2.35,04</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2287,25 +2287,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Lionel Nicolas Weissbrodt</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2.35,54</t>
+          <t>2.35,10</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>05.09.2021</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2322,25 +2322,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Einar Woldseth</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2.36,20</t>
+          <t>2.35,54</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>05.09.2021</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2357,25 +2357,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sondre Furmyr Johansen</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2.36,94</t>
+          <t>2.36,20</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>13.02.2022</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2392,25 +2392,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Arnt Martin Ystenes</t>
+          <t>Sondre Furmyr Johansen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2.37,19</t>
+          <t>2.36,94</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>13.02.2022</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kristin Myhr Pettersen</t>
+          <t>Arnt Martin Ystenes</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2.56,92</t>
+          <t>2.37,19</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>27.10.2013</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2462,25 +2462,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Kristin Myhr Pettersen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2.37,58</t>
+          <t>2.56,92</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>30.11.2024</t>
+          <t>27.10.2013</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2847,12 +2847,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Vegard S. Wigum</t>
+          <t>Jakob Isaksen</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2.43,40</t>
+          <t>2.43,38</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>05.12.2014</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jakob Isaksen</t>
+          <t>Vegard S. Wigum</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2.43,38</t>
+          <t>2.43,40</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>05.12.2014</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2917,25 +2917,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tor Arne Hegvik</t>
+          <t>Ludvig Svendsen</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2.44,94</t>
+          <t>2.43,55</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2952,20 +2952,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Vegard Maaø</t>
+          <t>Lin Carola Magdalene Nygren</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2.45,45</t>
+          <t>3.04,46</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19.09.2010</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2987,25 +2987,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Stian Olsen Sætervik</t>
+          <t>Tor Arne Hegvik</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2.45,66</t>
+          <t>2.44,94</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>21.10.2007</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3022,25 +3022,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ludvig Svendsen</t>
+          <t>Vegard Maaø</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2.45,91</t>
+          <t>2.45,45</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>19.09.2010</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3057,25 +3057,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Johannes Tryggestad</t>
+          <t>Stian Olsen Sætervik</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2.46,34</t>
+          <t>2.45,66</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>21.10.2007</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3092,25 +3092,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Reidar Lorentzen</t>
+          <t>Philip Giske Nyman</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2.46,22</t>
+          <t>2.45,95</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>16.03.2007</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3162,16 +3162,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Even Kristoffer Lind Bøckman</t>
+          <t>Johannes Tryggestad</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2.47,42</t>
+          <t>2.46,34</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3197,25 +3197,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Victor Voormolen Gutierrez</t>
+          <t>Reidar Lorentzen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.47,65</t>
+          <t>2.46,22</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>16.03.2007</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3232,25 +3232,25 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2.48,32</t>
+          <t>2.46,95</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>09.02.2008</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3267,20 +3267,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Vegard Skjervold</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2.48,14</t>
+          <t>2.47,04</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>21.01.2018</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3302,25 +3302,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Edvin Aurstad Bergum</t>
+          <t>Even Kristoffer Lind Bøckman</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2.48,20</t>
+          <t>2.47,42</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3337,20 +3337,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Thomas Stur Ekrem</t>
+          <t>Victor Voormolen Gutierrez</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.49,90</t>
+          <t>2.47,65</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01.10.2023</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3372,20 +3372,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ingjerd Jepsen Vegge</t>
+          <t>Ellen Kristine Eidsmo Hova</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3.11,52</t>
+          <t>3.07,85</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>12.02.2011</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3407,25 +3407,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Sondre Grimsmo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2.50,63</t>
+          <t>2.48,32</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>09.02.2008</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3442,25 +3442,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Anton Sergeevich Gorodkov</t>
+          <t>Vegard Skjervold</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2.51,30</t>
+          <t>2.48,14</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>07.02.2016</t>
+          <t>21.01.2018</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3477,16 +3477,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Brage Gylseth Dahl</t>
+          <t>Edvin Aurstad Bergum</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2.51,57</t>
+          <t>2.48,20</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3512,25 +3512,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Lin Carola Magdalene Nygren</t>
+          <t>Lev Shestov</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3.13,43</t>
+          <t>2.49,35</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3547,20 +3547,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Thomas Stur Ekrem</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2.52,06</t>
+          <t>2.49,90</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>01.10.2023</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3582,20 +3582,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jon Noé Høye</t>
+          <t>Ingjerd Jepsen Vegge</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2.52,67</t>
+          <t>3.11,52</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>12.02.2011</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3617,16 +3617,16 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ellen Kristine Eidsmo Hova</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3.14,72</t>
+          <t>2.50,63</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3652,25 +3652,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Anton Sergeevich Gorodkov</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2.53,23</t>
+          <t>2.51,30</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>07.02.2016</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3687,25 +3687,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sondre Aakerholm Adsen</t>
+          <t>Brage Gylseth Dahl</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2.53,61</t>
+          <t>2.51,57</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>06.04.2024</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3722,25 +3722,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Lyder Ringsvold Hogstad</t>
+          <t>Jon Noé Høye</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2.54,91</t>
+          <t>2.52,67</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3757,25 +3757,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Håkon Johansen</t>
+          <t>Sondre Aakerholm Adsen</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2.55,17</t>
+          <t>2.53,61</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>25.03.2006</t>
+          <t>06.04.2024</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3792,25 +3792,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Leander Gisvold Restad</t>
+          <t>Lyder Ringsvold Hogstad</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2.55,11</t>
+          <t>2.54,91</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3827,12 +3827,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Pedro Manquehual</t>
+          <t>Håkon Johansen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2.55,15</t>
+          <t>2.55,17</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>25.03.2006</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3862,25 +3862,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>David Fjeld</t>
+          <t>Leander Gisvold Restad</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2.55,80</t>
+          <t>2.55,11</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20.10.2007</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3897,25 +3897,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Njål Høie</t>
+          <t>Pedro Manquehual</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2.56,17</t>
+          <t>2.55,15</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>09.03.2014</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3932,25 +3932,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tony Christopher Moflag</t>
+          <t>David Fjeld</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2.56,83</t>
+          <t>2.55,80</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>20.10.2007</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3967,25 +3967,25 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Johan Mostervik</t>
+          <t>Njål Høie</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2.56,84</t>
+          <t>2.56,17</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>11.02.2018</t>
+          <t>09.03.2014</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4002,25 +4002,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Daniel Haugen Ngwenya</t>
+          <t>Tony Christopher Moflag</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2.56,97</t>
+          <t>2.56,83</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>19.04.2008</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4037,25 +4037,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Paal Aagaard</t>
+          <t>Johan Mostervik</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2.58,15</t>
+          <t>2.56,84</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>16.03.2007</t>
+          <t>11.02.2018</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4072,25 +4072,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kristian Myhr Høgstøl</t>
+          <t>Rasmus Larsen Natvig</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2.58,80</t>
+          <t>2.57,01</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4107,25 +4107,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Christian Dahle-Øfsti</t>
+          <t>Daniel Haugen Ngwenya</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2.58,85</t>
+          <t>2.56,97</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>27.10.2013</t>
+          <t>19.04.2008</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4142,25 +4142,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Morten Schanke</t>
+          <t>Paal Aagaard</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3.00,79</t>
+          <t>2.58,15</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>24.03.2017</t>
+          <t>16.03.2007</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4177,16 +4177,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tamer Saleh Abuzid</t>
+          <t>Kristian Myhr Høgstøl</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3.01,71</t>
+          <t>2.58,80</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -4212,25 +4212,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Christian Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3.01,97</t>
+          <t>2.58,85</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>27.10.2013</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4247,25 +4247,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Philip Giske Nyman</t>
+          <t>Morten Schanke</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3.04,05</t>
+          <t>3.00,79</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>24.03.2017</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4282,16 +4282,16 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sigurd Rodal Leirgulen</t>
+          <t>Tamer Saleh Abuzid</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3.05,72</t>
+          <t>3.01,71</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -4317,16 +4317,16 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Fredrik Holberg</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3.05,89</t>
+          <t>3.01,97</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -4352,25 +4352,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Eirik Ingeberg Garshol</t>
+          <t>Fredrik Holberg</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3.07,61</t>
+          <t>3.03,20</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>02.11.2024</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4387,25 +4387,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Dhanushi Attanapola</t>
+          <t>Liv Løfaldli</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3.32,09</t>
+          <t>3.25,89</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>23.05.2009</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4422,25 +4422,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Sigurd Rodal Leirgulen</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3.08,26</t>
+          <t>3.05,72</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>06.11.2010</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4457,25 +4457,25 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Isabel Ødegård Pedersen</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3.34,22</t>
+          <t>3.28,21</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4492,25 +4492,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ivan Erikovitch Alvestad</t>
+          <t>Eirik Ingeberg Garshol</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3.10,40</t>
+          <t>3.07,61</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>02.11.2024</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4527,25 +4527,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Gunhild Furuholt Valle</t>
+          <t>Dhanushi Attanapola</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3.34,81</t>
+          <t>3.32,09</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>23.05.2009</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4562,25 +4562,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Emily Liv Liem</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3.35,45</t>
+          <t>3.08,26</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>30.09.2019</t>
+          <t>06.11.2010</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4597,25 +4597,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Magnus Bakkejord</t>
+          <t>Isabel Ødegård Pedersen</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3.11,25</t>
+          <t>3.34,22</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>03.12.2011</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4632,25 +4632,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Magnus Svindland Næsgaard</t>
+          <t>Ivan Erikovitch Alvestad</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3.11,24</t>
+          <t>3.10,40</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>05.09.2021</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4667,25 +4667,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Gunhild Furuholt Valle</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3.12,22</t>
+          <t>3.34,81</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4702,25 +4702,25 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Rasmus Larsen Natvig</t>
+          <t>Magnus Svindland Næsgaard</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3.12,79</t>
+          <t>3.11,24</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>05.09.2021</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4737,25 +4737,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Liv Løfaldli</t>
+          <t>Emily Liv Liem</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3.38,89</t>
+          <t>3.35,45</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>30.09.2019</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4772,25 +4772,25 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Conrad Sippala Hassel</t>
+          <t>Magnus Bakkejord</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3.14,40</t>
+          <t>3.11,25</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>09.11.2019</t>
+          <t>03.12.2011</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4807,25 +4807,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ingeborg Strandenes</t>
+          <t>David Csejtey</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3.39,38</t>
+          <t>3.12,22</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4842,25 +4842,25 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kaan Baltaci</t>
+          <t>Conrad Sippala Hassel</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3.16,12</t>
+          <t>3.14,40</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>03.12.2022</t>
+          <t>09.11.2019</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4877,25 +4877,25 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Finn Øivind Fevang</t>
+          <t>Olav Høyland Hofstad</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3.17,09</t>
+          <t>3.15,38</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>14.01.2005</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4912,20 +4912,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>William Wale</t>
+          <t>Sigurd Øie Seland</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3.19,41</t>
+          <t>3.16,11</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>10.01.2014</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4947,25 +4947,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Oscar Kvaløy Tiller</t>
+          <t>Kaan Baltaci</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3.19,80</t>
+          <t>3.16,12</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20.11.2021</t>
+          <t>03.12.2022</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4982,25 +4982,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Anniken Skjøstad</t>
+          <t>Finn Øivind Fevang</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3.50,40</t>
+          <t>3.17,09</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>29.02.2020</t>
+          <t>14.01.2005</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5017,25 +5017,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>William Johannes Kirkelund Kristiansen</t>
+          <t>William Wale</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3.29,04</t>
+          <t>3.19,41</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20.03.2022</t>
+          <t>10.01.2014</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5052,25 +5052,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sigurd Øie Seland</t>
+          <t>Oscar Kvaløy Tiller</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3.30,17</t>
+          <t>3.19,80</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>20.11.2021</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5087,25 +5087,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Liem Emily Liv</t>
+          <t>Anniken Skjøstad</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3.58,15</t>
+          <t>3.50,40</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>29.02.2020</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5122,20 +5122,20 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Anton Hoel</t>
+          <t>Ruolai Liu</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3.31,67</t>
+          <t>3.50,85</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>07.12.2012</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5157,25 +5157,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Peder Lund Juul</t>
+          <t>William Johannes Kirkelund Kristiansen</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3.32,16</t>
+          <t>3.29,04</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>02.11.2024</t>
+          <t>20.03.2022</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5192,25 +5192,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sondre Thorgaard</t>
+          <t>Jesper Julius Sundseth Skjærli</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3.32,26</t>
+          <t>3.31,18</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5227,25 +5227,25 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jakob M. Tjøstheim</t>
+          <t>Anton Hoel</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>3.33,22</t>
+          <t>3.31,67</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20.04.2013</t>
+          <t>07.12.2012</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5262,25 +5262,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Thomas Paulsen</t>
+          <t>Liem Emily Liv</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3.33,80</t>
+          <t>3.58,15</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20.04.2013</t>
+          <t>28.10.2018</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5297,25 +5297,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Jesper Julius Sundseth Skjærli</t>
+          <t>Sondre Thorgaard</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3.33,74</t>
+          <t>3.32,26</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5332,25 +5332,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Angelico Mikkel Andersen</t>
+          <t>Peder Lund Juul</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3.34,23</t>
+          <t>3.32,16</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>29.02.2020</t>
+          <t>02.11.2024</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5367,25 +5367,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Robin von Bargen</t>
+          <t>Erik Solbakken Andersen</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3.35,04</t>
+          <t>3.32,16</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>23.05.2009</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5402,25 +5402,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Bernard Smuk</t>
+          <t>Jakob M. Tjøstheim</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3.36,13</t>
+          <t>3.33,22</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>20.04.2013</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5442,20 +5442,20 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3.36,81</t>
+          <t>3.33,64</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5472,25 +5472,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Marcus Thalberg Fagerheim</t>
+          <t>Thomas Paulsen</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3.38,40</t>
+          <t>3.33,80</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>20.04.2013</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5507,25 +5507,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Brage Kaminka Heiberg</t>
+          <t>Angelico Mikkel Andersen</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3.38,45</t>
+          <t>3.34,23</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>16.09.2023</t>
+          <t>29.02.2020</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5542,25 +5542,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Leo Alexander Farias Kristiansen</t>
+          <t>Robin von Bargen</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3.40,88</t>
+          <t>3.35,04</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>23.05.2009</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5577,25 +5577,25 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sigurd Kristoffersen Torvik</t>
+          <t>Bernard Smuk</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3.41,62</t>
+          <t>3.36,13</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5612,20 +5612,20 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Erik Solbakken Andersen</t>
+          <t>Lilly Fludal Osland</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3.45,15</t>
+          <t>4.01,60</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5647,20 +5647,20 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Jesper Øvermo Johansen</t>
+          <t>Brage Kaminka Heiberg</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3.44,62</t>
+          <t>3.38,45</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>16.09.2023</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5682,25 +5682,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Magnus Hestvik Larsen</t>
+          <t>Marcus Thalberg Fagerheim</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>3.45,07</t>
+          <t>3.38,40</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>14.02.2009</t>
+          <t>18.06.2011</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5717,25 +5717,25 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Vegard Olsvold</t>
+          <t>Leo Alexander Farias Kristiansen</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>3.50,05</t>
+          <t>3.40,88</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>29.02.2020</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5752,20 +5752,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Olav Høyland Hofstad</t>
+          <t>Ingeborg Vold Kirkvold</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3.52,09</t>
+          <t>4.07,71</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5787,20 +5787,20 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>André Prestmo-Edvardsen</t>
+          <t>Sigurd Kristoffersen Torvik</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3.52,92</t>
+          <t>3.41,62</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5822,25 +5822,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ingvar Høgås Wik</t>
+          <t>Jesper Øvermo Johansen</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3.56,03</t>
+          <t>3.44,62</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>23.11.2013</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5857,25 +5857,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Cornelius Wik</t>
+          <t>Magnus Hestvik Larsen</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>4.06,62</t>
+          <t>3.45,07</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>17.06.2023</t>
+          <t>14.02.2009</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5892,20 +5892,20 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Debik Isabella Johanne</t>
+          <t>Mikkel Fenstad</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>4.41,02</t>
+          <t>3.46,25</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5927,25 +5927,25 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Idun Skjærseth</t>
+          <t>Marius Gaup</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>4.42,77</t>
+          <t>3.48,65</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5962,25 +5962,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Filip Heuch</t>
+          <t>Vegard Olsvold</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4.22,63</t>
+          <t>3.50,05</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>29.02.2020</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5997,20 +5997,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Gajithsing Ajeethsing</t>
+          <t>André Prestmo-Edvardsen</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4.26,58</t>
+          <t>3.52,92</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6032,25 +6032,25 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Kasper Steen Jensen</t>
+          <t>Ingvar Høgås Wik</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4.29,32</t>
+          <t>3.56,03</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>23.11.2013</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6067,25 +6067,25 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Hans Otto Søyseth</t>
+          <t>Ragnhild Fjermestad</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4.31,19</t>
+          <t>4.33,80</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6102,20 +6102,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Theodor Hoff</t>
+          <t>Cornelius Wik</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4.34,98</t>
+          <t>4.06,62</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>17.06.2023</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6137,20 +6137,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Hauk Vold Kirkvold</t>
+          <t>Debik Isabella Johanne</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>4.38,12</t>
+          <t>4.41,02</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>28.10.2018</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6172,33 +6172,348 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
+          <t>Noah Kvam Haaheim</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>4.09,49</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>75</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>18.10.2025</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Verdal</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Idun Skjærseth</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>4.42,77</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>74</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>18.06.2011</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Filip Heuch</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>4.22,63</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>65</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>28.10.2018</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Gajithsing Ajeethsing</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>4.26,58</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>62</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>20.06.2021</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Kasper Steen Jensen</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>4.29,32</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>60</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>08.06.2024</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Hans Otto Søyseth</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>4.31,19</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>59</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>29.11.2014</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Theodor Hoff</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>4.34,98</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>56</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>03.11.2012</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Hauk Vold Kirkvold</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>4.38,12</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>54</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>17.04.2021</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>Einar Risholt Moen</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>4.43,46</t>
         </is>
       </c>
-      <c r="C165" t="n">
+      <c r="C173" t="n">
         <v>51</v>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>18.09.2011</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>Trondheim</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Brage Hetling</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>4.46,02</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>50</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -7868,12 +8183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Rasmus Larsen Natvig</t>
+          <t>Daniel Haugen Ngwenya</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3.04,75</t>
+          <t>3.04,82</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -7881,12 +8196,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15.06.2025</t>
+          <t>08.01.2008</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -7903,12 +8218,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Daniel Haugen Ngwenya</t>
+          <t>Rasmus Larsen Natvig</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3.04,82</t>
+          <t>3.04,75</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -7916,12 +8231,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>08.01.2008</t>
+          <t>15.06.2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -8218,12 +8533,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3.22,82</t>
+          <t>3.22,68</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -8231,12 +8546,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26.04.2008</t>
+          <t>16.06.2019</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -8253,12 +8568,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Ole Skuseth</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3.22,68</t>
+          <t>3.22,55</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -8288,12 +8603,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ole Skuseth</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.22,55</t>
+          <t>3.22,82</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -8301,12 +8616,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>16.06.2019</t>
+          <t>26.04.2008</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -8533,12 +8848,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Christian Dahle-Øfsti</t>
+          <t>Marit Søberg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3.45,51</t>
+          <t>4.08,26</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8546,12 +8861,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>09.04.2011</t>
+          <t>01.11.2008</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -8568,12 +8883,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Marit Søberg</t>
+          <t>Christian Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4.08,26</t>
+          <t>3.45,51</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -8581,12 +8896,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01.11.2008</t>
+          <t>09.04.2011</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -8856,7 +9171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G167"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8904,20 +9219,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.17,08</t>
+          <t>2.15,77</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.11.2023</t>
+          <t>14.11.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -9630,12 +9945,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Irja Gravdahl</t>
+          <t>Mila Maria Flåan</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.37,97</t>
+          <t>2.38,06</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -9643,12 +9958,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23.05.2009</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -9700,12 +10015,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mila Maria Flåan</t>
+          <t>Irja Gravdahl</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.38,06</t>
+          <t>2.37,97</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -9713,12 +10028,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>23.05.2009</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -10610,25 +10925,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Oline Skjønberg</t>
+          <t>Alexandra Contreras Jimenez</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.47,49</t>
+          <t>2.45,41</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10645,12 +10960,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Oline Skjønberg</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2.47,43</t>
+          <t>2.47,49</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -10658,7 +10973,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22.01.2010</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -10680,25 +10995,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sissel Furuholt Valle</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2.47,75</t>
+          <t>2.47,43</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>07.06.2025</t>
+          <t>22.01.2010</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10715,12 +11030,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ada Fludal Osland</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2.47,72</t>
+          <t>2.47,75</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -10728,12 +11043,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>07.06.2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Porsgrunn</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10750,20 +11065,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Heidi Elisabeth Ysland</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2.47,90</t>
+          <t>2.47,72</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12.02.2017</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -10785,12 +11100,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kirsti Bjørnsdatter Paulsen</t>
+          <t>Heidi Elisabeth Ysland</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2.47,97</t>
+          <t>2.47,90</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -10798,12 +11113,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>11.02.2018</t>
+          <t>12.02.2017</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10820,25 +11135,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Kirsti Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2.48,38</t>
+          <t>2.47,97</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>07.02.2016</t>
+          <t>11.02.2018</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10855,16 +11170,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Hedda Fosseng Traa</t>
+          <t>Thea Lervold Høffler</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2.48,61</t>
+          <t>2.48,38</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10890,25 +11205,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Carina Aadahl</t>
+          <t>Emre Vold Kirkvold</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2.49,25</t>
+          <t>2.29,48</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>11.12.2015</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -10925,25 +11240,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Inga Maren Steinsdotter Nestgaard</t>
+          <t>Hedda Fosseng Traa</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2.49,25</t>
+          <t>2.48,61</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>02.12.2017</t>
+          <t>07.02.2016</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -10960,25 +11275,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marthe Kalvik</t>
+          <t>Inga Maren Steinsdotter Nestgaard</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.49,46</t>
+          <t>2.49,25</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>24.03.2007</t>
+          <t>02.12.2017</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -10995,25 +11310,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hege Solberg Jørgensen</t>
+          <t>Carina Aadahl</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2.49,97</t>
+          <t>2.49,25</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12.02.2017</t>
+          <t>11.12.2015</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11030,25 +11345,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tage Singstad</t>
+          <t>Marthe Kalvik</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2.30,95</t>
+          <t>2.49,46</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>09.04.2011</t>
+          <t>24.03.2007</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11100,25 +11415,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Oda Sem Austmo</t>
+          <t>Hege Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2.50,10</t>
+          <t>2.49,97</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>12.02.2017</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -11135,25 +11450,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Torborg Duesten Blokkum</t>
+          <t>Tage Singstad</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2.50,18</t>
+          <t>2.30,95</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>13.03.2009</t>
+          <t>09.04.2011</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kirkenes</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -11170,12 +11485,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Thea Haugan</t>
+          <t>Oda Sem Austmo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2.50,12</t>
+          <t>2.50,10</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -11183,12 +11498,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -11205,25 +11520,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Erika Nicole Hagen</t>
+          <t>Torborg Duesten Blokkum</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2.50,27</t>
+          <t>2.50,18</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20.03.2022</t>
+          <t>13.03.2009</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Kirkenes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -11240,25 +11555,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Elisaveta Røste</t>
+          <t>Thea Haugan</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2.50,48</t>
+          <t>2.50,12</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -11275,25 +11590,25 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sigrid Eldholm</t>
+          <t>Erika Nicole Hagen</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2.50,75</t>
+          <t>2.50,27</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>20.03.2022</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -11310,20 +11625,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Emma Lu Tjeldvoll</t>
+          <t>Elisaveta Røste</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2.50,88</t>
+          <t>2.50,48</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -11345,20 +11660,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Linn Amalie Aresvik</t>
+          <t>Sigrid Eldholm</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2.51,16</t>
+          <t>2.50,75</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>07.10.2012</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11380,25 +11695,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Olea Winnberg</t>
+          <t>Emma Lu Tjeldvoll</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2.51,97</t>
+          <t>2.50,88</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -11415,25 +11730,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alexandra Contreras Jimenez</t>
+          <t>Linn Amalie Aresvik</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2.53,50</t>
+          <t>2.51,16</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>07.10.2012</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -11450,25 +11765,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Julie Hegvik</t>
+          <t>Olea Winnberg</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2.53,77</t>
+          <t>2.51,97</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>09.02.2008</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -11485,12 +11800,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nina Alicja Skarø</t>
+          <t>Julie Hegvik</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2.53,85</t>
+          <t>2.53,77</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -11498,12 +11813,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>12.02.2017</t>
+          <t>09.02.2008</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -11520,25 +11835,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Julie Wiik Arnesen</t>
+          <t>Nina Alicja Skarø</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2.54,22</t>
+          <t>2.53,85</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>12.02.2017</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -11555,25 +11870,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Dorottya Csejtey</t>
+          <t>Julie Wiik Arnesen</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2.54,62</t>
+          <t>2.54,22</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>12.02.2017</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -11590,25 +11905,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Marie Skuseth</t>
+          <t>Dorottya Csejtey</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2.54,80</t>
+          <t>2.54,62</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>12.02.2017</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -11625,20 +11940,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Annika Krill</t>
+          <t>Marie Skuseth</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.55,16</t>
+          <t>2.54,80</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>14.01.2005</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -11660,25 +11975,25 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Helene Marie Haram</t>
+          <t>Annika Krill</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2.55,85</t>
+          <t>2.55,16</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>24.10.2020</t>
+          <t>14.01.2005</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -11695,25 +12010,25 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Thora Bjarnøe Brandsegg</t>
+          <t>Helene Marie Haram</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2.55,94</t>
+          <t>2.55,85</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>02.10.2022</t>
+          <t>24.10.2020</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -11730,25 +12045,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Guro Rønningen Osmoen</t>
+          <t>Thora Bjarnøe Brandsegg</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2.56,35</t>
+          <t>2.55,94</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>02.10.2022</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -11765,25 +12080,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Hanne Søyseth</t>
+          <t>Guro Rønningen Osmoen</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.56,83</t>
+          <t>2.56,35</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>07.02.2016</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -11800,25 +12115,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Hanne Søyseth</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2.56,92</t>
+          <t>2.56,83</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>13.02.2022</t>
+          <t>07.02.2016</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -11835,25 +12150,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mari Helen Hammer</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2.57,09</t>
+          <t>2.56,92</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>14.01.2005</t>
+          <t>13.02.2022</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -11870,12 +12185,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Erle Kullerud Ytrehus</t>
+          <t>Mari Helen Hammer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2.57,13</t>
+          <t>2.57,09</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -11883,12 +12198,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>14.01.2005</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -11905,25 +12220,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Miriam Vedvik</t>
+          <t>Erle Kullerud Ytrehus</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2.57,89</t>
+          <t>2.57,13</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>09.02.2008</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -11940,25 +12255,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Isabella Johanne Debik</t>
+          <t>Miriam Vedvik</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.58,62</t>
+          <t>2.57,89</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20.03.2022</t>
+          <t>09.02.2008</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -11975,25 +12290,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ada Viken Refseth</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2.59,52</t>
+          <t>2.56,59</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -12010,25 +12325,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Silje Dahle</t>
+          <t>Isabella Johanne Debik</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2.59,95</t>
+          <t>2.58,62</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>20.03.2022</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -12045,25 +12360,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Marthe Eline Waagø-Hansen</t>
+          <t>Ada Viken Refseth</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3.00,38</t>
+          <t>2.59,52</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>17.04.2005</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -12080,25 +12395,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Aase Bjørnsdatter Paulsen</t>
+          <t>Silje Dahle</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3.00,93</t>
+          <t>2.59,95</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>07.02.2016</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -12115,25 +12430,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sunniva Belsnes</t>
+          <t>Marthe Eline Waagø-Hansen</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3.00,98</t>
+          <t>3.00,38</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>17.04.2005</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -12150,25 +12465,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Hedda Grimstad-Johannessen</t>
+          <t>Aase Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3.01,35</t>
+          <t>3.00,93</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>05.09.2021</t>
+          <t>07.02.2016</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -12185,20 +12500,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Olivia Sterud Prytz</t>
+          <t>Sunniva Belsnes</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3.01,56</t>
+          <t>3.00,98</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -12220,25 +12535,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Hansine Rindberg Monsø</t>
+          <t>Kristina Aleman Sandsund</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3.02,69</t>
+          <t>2.59,73</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -12255,25 +12570,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Anna Svendsen</t>
+          <t>Hedda Grimstad-Johannessen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3.02,71</t>
+          <t>3.01,35</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>05.09.2021</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -12290,20 +12605,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sara Skaalvik Trelstad</t>
+          <t>Olivia Sterud Prytz</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3.03,72</t>
+          <t>3.01,56</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>19.01.2014</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -12325,25 +12640,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Juliane-Linnea Tybell Svenum</t>
+          <t>Hansine Rindberg Monsø</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3.05,52</t>
+          <t>3.02,69</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>23.10.2021</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -12360,25 +12675,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Anna Svendsen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3.05,42</t>
+          <t>3.02,71</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -12395,25 +12710,25 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ingrid Johansen</t>
+          <t>Sofie Hepsø</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3.05,63</t>
+          <t>3.02,03</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>13.01.2007</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -12430,25 +12745,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Magne Petersen</t>
+          <t>Sara Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2.45,44</t>
+          <t>3.03,72</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>05.12.2014</t>
+          <t>19.01.2014</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -12465,25 +12780,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sofie Hoff</t>
+          <t>Michaela Josefin Abeleva Barrera</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3.07,50</t>
+          <t>3.03,80</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -12500,25 +12815,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Juliane-Linnea Tybell Svenum</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3.08,20</t>
+          <t>3.05,52</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>19.01.2014</t>
+          <t>23.10.2021</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -12535,20 +12850,20 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Helle Johnsen Selsås</t>
+          <t>Ingrid Johansen</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3.08,17</t>
+          <t>3.05,63</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>13.01.2007</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -12570,20 +12885,20 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Susanne Kolloen</t>
+          <t>Sofie Hoff</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3.08,08</t>
+          <t>3.04,18</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -12605,25 +12920,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Rune Larsen</t>
+          <t>Magne Petersen</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2.48,00</t>
+          <t>2.45,44</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>06.05.2023</t>
+          <t>05.12.2014</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarpsborg</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -12640,25 +12955,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Susanne Kolloen</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3.09,80</t>
+          <t>3.08,08</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -12675,20 +12990,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Hilde Stene Rygh</t>
+          <t>Helle Johnsen Selsås</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3.09,99</t>
+          <t>3.08,17</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>16.06.2012</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -12710,20 +13025,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ida Fiskaa Barstad</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3.10,24</t>
+          <t>3.08,20</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>19.01.2014</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -12745,25 +13060,25 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Helle Lundgren</t>
+          <t>Rune Larsen</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3.10,60</t>
+          <t>2.48,00</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>06.05.2023</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Sarpsborg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -12780,25 +13095,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Izabele Farias Ribeiro</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3.10,62</t>
+          <t>3.07,67</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>08.02.2015</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -12815,25 +13130,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sofie Hepsø</t>
+          <t>Chloe Branlat</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3.11,59</t>
+          <t>3.09,80</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -12850,20 +13165,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Elise Øystrøm Tyvold</t>
+          <t>Hilde Stene Rygh</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3.11,48</t>
+          <t>3.09,99</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>16.06.2012</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -12885,20 +13200,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Kine Marie Sørensen</t>
+          <t>Ida Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3.11,91</t>
+          <t>3.10,24</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>14.01.2005</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -12920,20 +13235,20 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ola vatn Gundersen</t>
+          <t>Helle Lundgren</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2.52,31</t>
+          <t>3.10,60</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20.01.2019</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -12955,25 +13270,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Selma Strandjord Lillerødvann</t>
+          <t>Izabele Farias Ribeiro</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3.14,11</t>
+          <t>3.10,62</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>08.02.2015</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -12990,25 +13305,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Aurora Alexandra Bjordal</t>
+          <t>Elise Øystrøm Tyvold</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3.14,27</t>
+          <t>3.11,48</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>05.09.2021</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13025,25 +13340,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Emre Vold Kirkvold</t>
+          <t>Kine Marie Sørensen</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2.52,81</t>
+          <t>3.11,91</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>14.01.2005</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13060,25 +13375,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Luma Nicole Farias Kristiansen</t>
+          <t>Elsa Dragsten Wake</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3.14,49</t>
+          <t>3.12,28</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>29.02.2020</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -13095,25 +13410,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Camila Dorao</t>
+          <t>Selma Strandjord Lillerødvann</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3.14,77</t>
+          <t>3.14,11</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -13130,20 +13445,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Alice Sophie Mittet</t>
+          <t>Ola vatn Gundersen</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3.18,64</t>
+          <t>2.52,31</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>21.01.2018</t>
+          <t>20.01.2019</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -13165,25 +13480,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Aurora S. Juel</t>
+          <t>Aurora Alexandra Bjordal</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3.18,86</t>
+          <t>3.14,27</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>16.06.2012</t>
+          <t>05.09.2021</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -13200,25 +13515,25 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Alisa Kulagina</t>
+          <t>Luma Nicole Farias Kristiansen</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3.19,53</t>
+          <t>3.14,49</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>29.02.2020</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -13235,25 +13550,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Elsa Dragsten Wake</t>
+          <t>Camila Dorao</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3.19,77</t>
+          <t>3.14,77</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>22.02.2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -13270,25 +13585,25 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Michaela Josefin Abeleva Barrera</t>
+          <t>Alice Sophie Mittet</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3.20,25</t>
+          <t>3.18,64</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>21.01.2018</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -13305,25 +13620,25 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Amalie Gylseth Dahl</t>
+          <t>Aurora S. Juel</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3.20,50</t>
+          <t>3.18,86</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>02.12.2023</t>
+          <t>16.06.2012</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -13340,25 +13655,25 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sofia Bjørklund Mora</t>
+          <t>Amalie Gylseth Dahl</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3.20,86</t>
+          <t>3.20,50</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>02.12.2023</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -13375,25 +13690,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Synnøve Fevang</t>
+          <t>Sofia Bjørklund Mora</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3.22,06</t>
+          <t>3.20,86</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>25.03.2006</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -13410,25 +13725,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Line Steine Bertelsen</t>
+          <t>Synnøve Fevang</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3.22,89</t>
+          <t>3.22,06</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20.11.2021</t>
+          <t>25.03.2006</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -13445,25 +13760,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Madeleine Tran Wæraas</t>
+          <t>Line Steine Bertelsen</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3.23,55</t>
+          <t>3.22,89</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>30.09.2019</t>
+          <t>20.11.2021</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -13480,25 +13795,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Amalie Solvoll</t>
+          <t>Madeleine Tran Wæraas</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3.24,62</t>
+          <t>3.23,55</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>30.09.2019</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -13515,25 +13830,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sigrid Moen Henriksen</t>
+          <t>Amalie Solvoll</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3.26,35</t>
+          <t>3.24,62</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -13550,25 +13865,25 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Julia Tan</t>
+          <t>Sigrid Moen Henriksen</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3.30,14</t>
+          <t>3.26,35</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>18.04.2009</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -13585,25 +13900,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Cathrine Hegle</t>
+          <t>Julia Tan</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3.30,57</t>
+          <t>3.30,14</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>12.02.2011</t>
+          <t>18.04.2009</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -13620,25 +13935,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Emilie Sandvik Gangåssæter</t>
+          <t>Cathrine Hegle</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3.31,32</t>
+          <t>3.30,57</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>12.02.2011</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -13655,25 +13970,25 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Arne Martin Einarsrud Rismoen</t>
+          <t>Emilie Sandvik Gangåssæter</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>3.08,95</t>
+          <t>3.31,32</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -13725,20 +14040,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Lea almaas</t>
+          <t>Arne Martin Einarsrud Rismoen</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3.37,26</t>
+          <t>3.08,95</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>22.01.2012</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -13760,25 +14075,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Mia Bretun Finserå</t>
+          <t>Hedda Gätzschmann</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3.40,24</t>
+          <t>3.35,05</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -13795,25 +14110,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Hedda Gätzschmann</t>
+          <t>Lea almaas</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3.43,39</t>
+          <t>3.37,26</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>22.01.2012</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -13830,25 +14145,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Marie Wærnes Blom</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3.44,18</t>
+          <t>3.35,91</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -13865,25 +14180,25 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Julia Beatrice Ferreira Kristiansen</t>
+          <t>Mia Bretun Finserå</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3.44,14</t>
+          <t>3.40,24</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>03.12.2016</t>
+          <t>03.11.2012</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -13900,25 +14215,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ingrid Skye Naustvoll</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3.46,38</t>
+          <t>3.40,34</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20.04.2013</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -13935,25 +14250,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Louise Thys</t>
+          <t>Julia Beatrice Ferreira Kristiansen</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3.46,22</t>
+          <t>3.44,14</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>03.12.2016</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -13970,25 +14285,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Elina Arefjord Spangelo</t>
+          <t>Marie Wærnes Blom</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3.50,33</t>
+          <t>3.44,18</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -14005,20 +14320,20 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tora Tveiten</t>
+          <t>Ingrid Skye Naustvoll</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3.52,36</t>
+          <t>3.46,38</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>20.04.2013</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -14045,15 +14360,15 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3.55,52</t>
+          <t>3.45,99</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -14075,20 +14390,20 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ronja Emilia Wikström</t>
+          <t>Charlotte Talseth</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3.57,90</t>
+          <t>3.46,18</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>17.06.2023</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -14110,25 +14425,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Else Malin Meidal</t>
+          <t>Live Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4.00,90</t>
+          <t>3.46,49</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>28.10.2012</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -14145,20 +14460,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ramona Vutudal</t>
+          <t>Tora Tveiten</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4.02,13</t>
+          <t>3.52,36</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>19.04.2008</t>
+          <t>29.11.2014</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -14180,25 +14495,25 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Amelia Roaldseth</t>
+          <t>Ronja Emilia Wikström</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4.04,82</t>
+          <t>3.57,90</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>19.04.2008</t>
+          <t>17.06.2023</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -14215,25 +14530,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Aida Smalø Moen</t>
+          <t>Else Malin Meidal</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>4.05,96</t>
+          <t>4.00,90</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>29.10.2011</t>
+          <t>28.10.2012</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -14250,25 +14565,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Anna Fenstad Høysæter</t>
+          <t>Ramona Vutudal</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4.17,88</t>
+          <t>4.02,13</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>19.04.2008</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -14285,20 +14600,20 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Kristina Bragadottir</t>
+          <t>Amelia Roaldseth</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>4.22,47</t>
+          <t>4.04,82</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>03.12.2011</t>
+          <t>19.04.2008</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -14320,25 +14635,25 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Aurora Dahl Bere</t>
+          <t>Aida Smalø Moen</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>4.22,73</t>
+          <t>4.05,96</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>10.02.2024</t>
+          <t>29.10.2011</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -14355,20 +14670,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sunniva Eldholm</t>
+          <t>Ilaria Kari Cherubini</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>4.24,04</t>
+          <t>4.06,64</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14390,25 +14705,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Hedda Larsen Natvig</t>
+          <t>Sara Olea  Riseth Moe</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4.23,88</t>
+          <t>4.12,09</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>16.09.2023</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -14425,20 +14740,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Camilla Gervasoni</t>
+          <t>Anna Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4.25,19</t>
+          <t>4.17,88</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14460,25 +14775,25 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Jassmitha Ajeethsing</t>
+          <t>Emilie Magnussen</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4.25,33</t>
+          <t>4.15,50</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>29.02.2020</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -14495,20 +14810,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Connie Rakel Lånke</t>
+          <t>Kristina Bragadottir</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4.27,50</t>
+          <t>4.22,47</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>05.04.2014</t>
+          <t>03.12.2011</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14530,25 +14845,25 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Elena Fyhn Leida</t>
+          <t>Aurora Dahl Bere</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4.34,37</t>
+          <t>4.22,73</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>10.02.2024</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -14565,20 +14880,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Frida Merethe Norli Eidsvåg</t>
+          <t>Sunniva Eldholm</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>4.42,67</t>
+          <t>4.24,04</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14600,25 +14915,25 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sigrid Gylseth Dahl</t>
+          <t>Hedda Larsen Natvig</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>4.55,15</t>
+          <t>4.23,88</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>06.04.2024</t>
+          <t>16.09.2023</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -14635,25 +14950,25 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Aida Sofie Feyzi</t>
+          <t>Jassmitha Ajeethsing</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>4.56,05</t>
+          <t>4.25,33</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>29.02.2020</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -14670,33 +14985,313 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
+          <t>Camilla Gervasoni</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>4.25,19</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>90</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>16.09.2012</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Oda Brennhaug Tangen</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>4.23,41</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>89</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Connie Rakel Lånke</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>4.27,50</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>87</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>05.04.2014</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Elena Fyhn Leida</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>4.34,37</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>81</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>20.06.2021</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Frida Merethe Norli Eidsvåg</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>4.42,67</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>74</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>21.06.2014</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Shiva Sattanathan</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>4.16,07</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>70</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>29.11.2025</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sigrid Gylseth Dahl</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>4.55,15</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>65</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>06.04.2024</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Aida Sofie Feyzi</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>4.56,05</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>64</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>28.10.2018</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
           <t>Phoebe Thalberg Fagerheim</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>4.57,29</t>
         </is>
       </c>
-      <c r="C167" t="n">
+      <c r="C175" t="n">
         <v>64</v>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>18.09.2011</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>Trondheim</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -15561,12 +16156,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marthe Kalvik</t>
+          <t>Frøydis Vatn Andersen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.53,11</t>
+          <t>2.53,18</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -15574,12 +16169,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>04.11.2007</t>
+          <t>11.06.2017</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -15596,12 +16191,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Frøydis Vatn Andersen</t>
+          <t>Marthe Kalvik</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2.53,18</t>
+          <t>2.53,11</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -15609,12 +16204,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11.06.2017</t>
+          <t>04.11.2007</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -16191,12 +16786,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kristina Elena Bjørklund Mora</t>
+          <t>Live Killingberg Sandberg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3.02,87</t>
+          <t>3.02,91</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -16204,12 +16799,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>12.06.2010</t>
+          <t>31.03.2019</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -16261,12 +16856,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Live Killingberg Sandberg</t>
+          <t>Kristina Elena Bjørklund Mora</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3.02,91</t>
+          <t>3.02,87</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -16274,12 +16869,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>31.03.2019</t>
+          <t>12.06.2010</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -17171,12 +17766,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Emilie Sandvik Gangåssæter</t>
+          <t>Ida Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3.28,16</t>
+          <t>3.27,92</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -17206,12 +17801,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ida Fiskaa Barstad</t>
+          <t>Emilie Sandvik Gangåssæter</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3.27,92</t>
+          <t>3.28,16</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -17766,12 +18361,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Aurora Alexandra Bjordal</t>
+          <t>Sigrid Gylseth Dahl</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>4.06,59</t>
+          <t>4.06,29</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -17779,12 +18374,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>28.04.2018</t>
+          <t>15.06.2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17801,12 +18396,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sigrid Gylseth Dahl</t>
+          <t>Aurora Alexandra Bjordal</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4.06,29</t>
+          <t>4.06,59</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -17814,12 +18409,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>15.06.2025</t>
+          <t>28.04.2018</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
